--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/NEW_YORK_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/NEW_YORK_2024.xlsx
@@ -6954,7 +6954,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C367">
@@ -20706,7 +20706,7 @@
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1131">
